--- a/상습결빙지역.xlsx
+++ b/상습결빙지역.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2138" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2138" uniqueCount="616">
   <si>
     <t>순번</t>
   </si>
@@ -366,9 +366,6 @@
     <t>군산시 소룡동 일반국도</t>
   </si>
   <si>
-    <t>광산구</t>
-  </si>
-  <si>
     <t>명도동</t>
   </si>
   <si>
@@ -621,9 +618,6 @@
     <t>광산구 비아동 광역시도</t>
   </si>
   <si>
-    <t>서구</t>
-  </si>
-  <si>
     <t>치평동</t>
   </si>
   <si>
@@ -708,9 +702,6 @@
     <t>정읍시 하북동 고속국도</t>
   </si>
   <si>
-    <t>북구</t>
-  </si>
-  <si>
     <t>동림동</t>
   </si>
   <si>
@@ -769,9 +760,6 @@
   </si>
   <si>
     <t>익산시 웅포면 지방도</t>
-  </si>
-  <si>
-    <t>남구</t>
   </si>
   <si>
     <t>양과동</t>
@@ -1831,6 +1819,86 @@
   </si>
   <si>
     <t>전남광주통합특별시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광주서구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광주서구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광주서구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광주남구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광주남구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광주북구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광주북구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광주북구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광주북구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광주북구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광주북구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광주북구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광주광산구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광주광산구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광주광산구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광주광산구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광주광산구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광주광산구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광주광산구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광주광산구</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2215,7 +2283,7 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
@@ -2241,7 +2309,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
@@ -2319,7 +2387,7 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -2345,7 +2413,7 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="D7" t="s">
         <v>25</v>
@@ -2371,7 +2439,7 @@
         <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="D8" t="s">
         <v>25</v>
@@ -2397,7 +2465,7 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D9" t="s">
         <v>25</v>
@@ -2423,7 +2491,7 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D10" t="s">
         <v>25</v>
@@ -2449,7 +2517,7 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="D11" t="s">
         <v>25</v>
@@ -2475,7 +2543,7 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D12" t="s">
         <v>25</v>
@@ -2501,7 +2569,7 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D13" t="s">
         <v>25</v>
@@ -2527,7 +2595,7 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="D14" t="s">
         <v>25</v>
@@ -2553,7 +2621,7 @@
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="D15" t="s">
         <v>25</v>
@@ -2579,7 +2647,7 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D16" t="s">
         <v>25</v>
@@ -2605,7 +2673,7 @@
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D17" t="s">
         <v>25</v>
@@ -2631,7 +2699,7 @@
         <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D18" t="s">
         <v>25</v>
@@ -2657,7 +2725,7 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D19" t="s">
         <v>25</v>
@@ -2683,7 +2751,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="D20" t="s">
         <v>25</v>
@@ -2709,7 +2777,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="D21" t="s">
         <v>25</v>
@@ -2735,7 +2803,7 @@
         <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D22" t="s">
         <v>25</v>
@@ -2761,7 +2829,7 @@
         <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D23" t="s">
         <v>25</v>
@@ -2787,7 +2855,7 @@
         <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D24" t="s">
         <v>25</v>
@@ -2813,7 +2881,7 @@
         <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="D25" t="s">
         <v>25</v>
@@ -2839,7 +2907,7 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="D26" t="s">
         <v>25</v>
@@ -2865,7 +2933,7 @@
         <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D27" t="s">
         <v>25</v>
@@ -2891,7 +2959,7 @@
         <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="D28" t="s">
         <v>25</v>
@@ -2917,7 +2985,7 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D29" t="s">
         <v>25</v>
@@ -2943,7 +3011,7 @@
         <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D30" t="s">
         <v>25</v>
@@ -2969,7 +3037,7 @@
         <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D31" t="s">
         <v>25</v>
@@ -2995,7 +3063,7 @@
         <v>8</v>
       </c>
       <c r="C32" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D32" t="s">
         <v>25</v>
@@ -3021,7 +3089,7 @@
         <v>8</v>
       </c>
       <c r="C33" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D33" t="s">
         <v>25</v>
@@ -3047,7 +3115,7 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D34" t="s">
         <v>25</v>
@@ -3073,7 +3141,7 @@
         <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D35" t="s">
         <v>25</v>
@@ -3099,7 +3167,7 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D36" t="s">
         <v>25</v>
@@ -3125,7 +3193,7 @@
         <v>8</v>
       </c>
       <c r="C37" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D37" t="s">
         <v>25</v>
@@ -3151,7 +3219,7 @@
         <v>8</v>
       </c>
       <c r="C38" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D38" t="s">
         <v>25</v>
@@ -3177,7 +3245,7 @@
         <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D39" t="s">
         <v>25</v>
@@ -3203,7 +3271,7 @@
         <v>8</v>
       </c>
       <c r="C40" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="D40" t="s">
         <v>25</v>
@@ -3229,7 +3297,7 @@
         <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="D41" t="s">
         <v>25</v>
@@ -3255,7 +3323,7 @@
         <v>8</v>
       </c>
       <c r="C42" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D42" t="s">
         <v>25</v>
@@ -3281,7 +3349,7 @@
         <v>8</v>
       </c>
       <c r="C43" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="D43" t="s">
         <v>25</v>
@@ -3307,7 +3375,7 @@
         <v>8</v>
       </c>
       <c r="C44" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="D44" t="s">
         <v>25</v>
@@ -3333,7 +3401,7 @@
         <v>8</v>
       </c>
       <c r="C45" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D45" t="s">
         <v>25</v>
@@ -3359,7 +3427,7 @@
         <v>8</v>
       </c>
       <c r="C46" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D46" t="s">
         <v>25</v>
@@ -3385,7 +3453,7 @@
         <v>8</v>
       </c>
       <c r="C47" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D47" t="s">
         <v>51</v>
@@ -3411,7 +3479,7 @@
         <v>8</v>
       </c>
       <c r="C48" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="D48" t="s">
         <v>51</v>
@@ -3437,7 +3505,7 @@
         <v>8</v>
       </c>
       <c r="C49" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D49" t="s">
         <v>51</v>
@@ -3463,7 +3531,7 @@
         <v>8</v>
       </c>
       <c r="C50" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D50" t="s">
         <v>9</v>
@@ -3489,7 +3557,7 @@
         <v>8</v>
       </c>
       <c r="C51" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D51" t="s">
         <v>57</v>
@@ -3567,7 +3635,7 @@
         <v>8</v>
       </c>
       <c r="C54" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D54" t="s">
         <v>9</v>
@@ -3645,7 +3713,7 @@
         <v>8</v>
       </c>
       <c r="C57" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D57" t="s">
         <v>57</v>
@@ -3723,7 +3791,7 @@
         <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D60" t="s">
         <v>9</v>
@@ -3749,7 +3817,7 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D61" t="s">
         <v>9</v>
@@ -3775,7 +3843,7 @@
         <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D62" t="s">
         <v>57</v>
@@ -3801,7 +3869,7 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D63" t="s">
         <v>78</v>
@@ -3879,7 +3947,7 @@
         <v>8</v>
       </c>
       <c r="C66" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D66" t="s">
         <v>87</v>
@@ -4191,7 +4259,7 @@
         <v>8</v>
       </c>
       <c r="C78" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D78" t="s">
         <v>101</v>
@@ -4269,7 +4337,7 @@
         <v>8</v>
       </c>
       <c r="C81" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="D81" t="s">
         <v>109</v>
@@ -4321,16 +4389,16 @@
         <v>8</v>
       </c>
       <c r="C83" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="D83" t="s">
+        <v>608</v>
+      </c>
+      <c r="E83" t="s">
         <v>114</v>
       </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
         <v>115</v>
-      </c>
-      <c r="F83" t="s">
-        <v>116</v>
       </c>
       <c r="G83">
         <v>35.16763889192562</v>
@@ -4353,10 +4421,10 @@
         <v>81</v>
       </c>
       <c r="E84" t="s">
+        <v>116</v>
+      </c>
+      <c r="F84" t="s">
         <v>117</v>
-      </c>
-      <c r="F84" t="s">
-        <v>118</v>
       </c>
       <c r="G84">
         <v>35.625628846409043</v>
@@ -4373,16 +4441,16 @@
         <v>8</v>
       </c>
       <c r="C85" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D85" t="s">
+        <v>118</v>
+      </c>
+      <c r="E85" t="s">
         <v>119</v>
       </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
         <v>120</v>
-      </c>
-      <c r="F85" t="s">
-        <v>121</v>
       </c>
       <c r="G85">
         <v>34.492003809711107</v>
@@ -4405,10 +4473,10 @@
         <v>84</v>
       </c>
       <c r="E86" t="s">
+        <v>121</v>
+      </c>
+      <c r="F86" t="s">
         <v>122</v>
-      </c>
-      <c r="F86" t="s">
-        <v>123</v>
       </c>
       <c r="G86">
         <v>35.380657077059027</v>
@@ -4431,10 +4499,10 @@
         <v>106</v>
       </c>
       <c r="E87" t="s">
+        <v>123</v>
+      </c>
+      <c r="F87" t="s">
         <v>124</v>
-      </c>
-      <c r="F87" t="s">
-        <v>125</v>
       </c>
       <c r="G87">
         <v>35.969765878273478</v>
@@ -4457,10 +4525,10 @@
         <v>106</v>
       </c>
       <c r="E88" t="s">
+        <v>125</v>
+      </c>
+      <c r="F88" t="s">
         <v>126</v>
-      </c>
-      <c r="F88" t="s">
-        <v>127</v>
       </c>
       <c r="G88">
         <v>35.956249217825103</v>
@@ -4477,16 +4545,16 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D89" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E89" t="s">
+        <v>127</v>
+      </c>
+      <c r="F89" t="s">
         <v>128</v>
-      </c>
-      <c r="F89" t="s">
-        <v>129</v>
       </c>
       <c r="G89">
         <v>34.564457080444541</v>
@@ -4506,13 +4574,13 @@
         <v>15</v>
       </c>
       <c r="D90" t="s">
+        <v>129</v>
+      </c>
+      <c r="E90" t="s">
         <v>130</v>
       </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
         <v>131</v>
-      </c>
-      <c r="F90" t="s">
-        <v>132</v>
       </c>
       <c r="G90">
         <v>35.856325878878813</v>
@@ -4529,16 +4597,16 @@
         <v>8</v>
       </c>
       <c r="C91" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D91" t="s">
-        <v>114</v>
+        <v>609</v>
       </c>
       <c r="E91" t="s">
+        <v>132</v>
+      </c>
+      <c r="F91" t="s">
         <v>133</v>
-      </c>
-      <c r="F91" t="s">
-        <v>134</v>
       </c>
       <c r="G91">
         <v>35.158723441594319</v>
@@ -4555,16 +4623,16 @@
         <v>8</v>
       </c>
       <c r="C92" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="D92" t="s">
-        <v>114</v>
+        <v>610</v>
       </c>
       <c r="E92" t="s">
+        <v>134</v>
+      </c>
+      <c r="F92" t="s">
         <v>135</v>
-      </c>
-      <c r="F92" t="s">
-        <v>136</v>
       </c>
       <c r="G92">
         <v>35.153729187393417</v>
@@ -4581,16 +4649,16 @@
         <v>8</v>
       </c>
       <c r="C93" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D93" t="s">
-        <v>114</v>
+        <v>610</v>
       </c>
       <c r="E93" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F93" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G93">
         <v>35.153002057170582</v>
@@ -4607,16 +4675,16 @@
         <v>8</v>
       </c>
       <c r="C94" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="D94" t="s">
         <v>101</v>
       </c>
       <c r="E94" t="s">
+        <v>137</v>
+      </c>
+      <c r="F94" t="s">
         <v>138</v>
-      </c>
-      <c r="F94" t="s">
-        <v>139</v>
       </c>
       <c r="G94">
         <v>34.761610731484772</v>
@@ -4633,16 +4701,16 @@
         <v>8</v>
       </c>
       <c r="C95" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D95" t="s">
         <v>101</v>
       </c>
       <c r="E95" t="s">
+        <v>139</v>
+      </c>
+      <c r="F95" t="s">
         <v>140</v>
-      </c>
-      <c r="F95" t="s">
-        <v>141</v>
       </c>
       <c r="G95">
         <v>34.815105345751753</v>
@@ -4665,10 +4733,10 @@
         <v>84</v>
       </c>
       <c r="E96" t="s">
+        <v>141</v>
+      </c>
+      <c r="F96" t="s">
         <v>142</v>
-      </c>
-      <c r="F96" t="s">
-        <v>143</v>
       </c>
       <c r="G96">
         <v>35.420746962552833</v>
@@ -4685,16 +4753,16 @@
         <v>8</v>
       </c>
       <c r="C97" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D97" t="s">
-        <v>114</v>
+        <v>610</v>
       </c>
       <c r="E97" t="s">
+        <v>143</v>
+      </c>
+      <c r="F97" t="s">
         <v>144</v>
-      </c>
-      <c r="F97" t="s">
-        <v>145</v>
       </c>
       <c r="G97">
         <v>35.220626715056298</v>
@@ -4717,10 +4785,10 @@
         <v>84</v>
       </c>
       <c r="E98" t="s">
+        <v>141</v>
+      </c>
+      <c r="F98" t="s">
         <v>142</v>
-      </c>
-      <c r="F98" t="s">
-        <v>143</v>
       </c>
       <c r="G98">
         <v>35.422752763567743</v>
@@ -4737,7 +4805,7 @@
         <v>8</v>
       </c>
       <c r="C99" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D99" t="s">
         <v>12</v>
@@ -4746,7 +4814,7 @@
         <v>13</v>
       </c>
       <c r="F99" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G99">
         <v>34.334825443925752</v>
@@ -4763,16 +4831,16 @@
         <v>8</v>
       </c>
       <c r="C100" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="D100" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E100" t="s">
+        <v>146</v>
+      </c>
+      <c r="F100" t="s">
         <v>147</v>
-      </c>
-      <c r="F100" t="s">
-        <v>148</v>
       </c>
       <c r="G100">
         <v>34.739371971244047</v>
@@ -4789,16 +4857,16 @@
         <v>8</v>
       </c>
       <c r="C101" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D101" t="s">
-        <v>114</v>
+        <v>610</v>
       </c>
       <c r="E101" t="s">
+        <v>143</v>
+      </c>
+      <c r="F101" t="s">
         <v>144</v>
-      </c>
-      <c r="F101" t="s">
-        <v>145</v>
       </c>
       <c r="G101">
         <v>35.218637910340462</v>
@@ -4821,10 +4889,10 @@
         <v>106</v>
       </c>
       <c r="E102" t="s">
+        <v>148</v>
+      </c>
+      <c r="F102" t="s">
         <v>149</v>
-      </c>
-      <c r="F102" t="s">
-        <v>150</v>
       </c>
       <c r="G102">
         <v>35.979194905326779</v>
@@ -4844,13 +4912,13 @@
         <v>15</v>
       </c>
       <c r="D103" t="s">
+        <v>129</v>
+      </c>
+      <c r="E103" t="s">
         <v>130</v>
       </c>
-      <c r="E103" t="s">
-        <v>131</v>
-      </c>
       <c r="F103" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G103">
         <v>35.862492426584787</v>
@@ -4873,10 +4941,10 @@
         <v>106</v>
       </c>
       <c r="E104" t="s">
+        <v>151</v>
+      </c>
+      <c r="F104" t="s">
         <v>152</v>
-      </c>
-      <c r="F104" t="s">
-        <v>153</v>
       </c>
       <c r="G104">
         <v>36.014741727116977</v>
@@ -4893,16 +4961,16 @@
         <v>8</v>
       </c>
       <c r="C105" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D105" t="s">
-        <v>114</v>
+        <v>611</v>
       </c>
       <c r="E105" t="s">
+        <v>153</v>
+      </c>
+      <c r="F105" t="s">
         <v>154</v>
-      </c>
-      <c r="F105" t="s">
-        <v>155</v>
       </c>
       <c r="G105">
         <v>35.146957076599193</v>
@@ -4919,16 +4987,16 @@
         <v>8</v>
       </c>
       <c r="C106" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D106" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E106" t="s">
+        <v>155</v>
+      </c>
+      <c r="F106" t="s">
         <v>156</v>
-      </c>
-      <c r="F106" t="s">
-        <v>157</v>
       </c>
       <c r="G106">
         <v>34.76870993065863</v>
@@ -4951,10 +5019,10 @@
         <v>106</v>
       </c>
       <c r="E107" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F107" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G107">
         <v>36.020656163115987</v>
@@ -4971,16 +5039,16 @@
         <v>8</v>
       </c>
       <c r="C108" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D108" t="s">
         <v>109</v>
       </c>
       <c r="E108" t="s">
+        <v>158</v>
+      </c>
+      <c r="F108" t="s">
         <v>159</v>
-      </c>
-      <c r="F108" t="s">
-        <v>160</v>
       </c>
       <c r="G108">
         <v>35.012868067587988</v>
@@ -5003,10 +5071,10 @@
         <v>106</v>
       </c>
       <c r="E109" t="s">
+        <v>160</v>
+      </c>
+      <c r="F109" t="s">
         <v>161</v>
-      </c>
-      <c r="F109" t="s">
-        <v>162</v>
       </c>
       <c r="G109">
         <v>35.942999337006853</v>
@@ -5023,16 +5091,16 @@
         <v>8</v>
       </c>
       <c r="C110" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="D110" t="s">
-        <v>114</v>
+        <v>612</v>
       </c>
       <c r="E110" t="s">
+        <v>162</v>
+      </c>
+      <c r="F110" t="s">
         <v>163</v>
-      </c>
-      <c r="F110" t="s">
-        <v>164</v>
       </c>
       <c r="G110">
         <v>35.073779437767129</v>
@@ -5049,16 +5117,16 @@
         <v>8</v>
       </c>
       <c r="C111" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D111" t="s">
         <v>101</v>
       </c>
       <c r="E111" t="s">
+        <v>164</v>
+      </c>
+      <c r="F111" t="s">
         <v>165</v>
-      </c>
-      <c r="F111" t="s">
-        <v>166</v>
       </c>
       <c r="G111">
         <v>34.841054435082548</v>
@@ -5075,16 +5143,16 @@
         <v>8</v>
       </c>
       <c r="C112" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="D112" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E112" t="s">
+        <v>166</v>
+      </c>
+      <c r="F112" t="s">
         <v>167</v>
-      </c>
-      <c r="F112" t="s">
-        <v>168</v>
       </c>
       <c r="G112">
         <v>34.660650529649352</v>
@@ -5101,16 +5169,16 @@
         <v>8</v>
       </c>
       <c r="C113" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="D113" t="s">
-        <v>114</v>
+        <v>613</v>
       </c>
       <c r="E113" t="s">
+        <v>168</v>
+      </c>
+      <c r="F113" t="s">
         <v>169</v>
-      </c>
-      <c r="F113" t="s">
-        <v>170</v>
       </c>
       <c r="G113">
         <v>35.120766769124387</v>
@@ -5130,13 +5198,13 @@
         <v>15</v>
       </c>
       <c r="D114" t="s">
+        <v>170</v>
+      </c>
+      <c r="E114" t="s">
         <v>171</v>
       </c>
-      <c r="E114" t="s">
+      <c r="F114" t="s">
         <v>172</v>
-      </c>
-      <c r="F114" t="s">
-        <v>173</v>
       </c>
       <c r="G114">
         <v>35.488060390473713</v>
@@ -5153,16 +5221,16 @@
         <v>8</v>
       </c>
       <c r="C115" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="D115" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E115" t="s">
+        <v>146</v>
+      </c>
+      <c r="F115" t="s">
         <v>147</v>
-      </c>
-      <c r="F115" t="s">
-        <v>148</v>
       </c>
       <c r="G115">
         <v>34.672294705999391</v>
@@ -5185,10 +5253,10 @@
         <v>106</v>
       </c>
       <c r="E116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F116" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G116">
         <v>35.988579194548549</v>
@@ -5205,16 +5273,16 @@
         <v>8</v>
       </c>
       <c r="C117" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D117" t="s">
+        <v>173</v>
+      </c>
+      <c r="E117" t="s">
         <v>174</v>
       </c>
-      <c r="E117" t="s">
+      <c r="F117" t="s">
         <v>175</v>
-      </c>
-      <c r="F117" t="s">
-        <v>176</v>
       </c>
       <c r="G117">
         <v>35.269744255095191</v>
@@ -5237,10 +5305,10 @@
         <v>106</v>
       </c>
       <c r="E118" t="s">
+        <v>151</v>
+      </c>
+      <c r="F118" t="s">
         <v>152</v>
-      </c>
-      <c r="F118" t="s">
-        <v>153</v>
       </c>
       <c r="G118">
         <v>35.980845050989799</v>
@@ -5257,16 +5325,16 @@
         <v>8</v>
       </c>
       <c r="C119" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D119" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E119" t="s">
+        <v>155</v>
+      </c>
+      <c r="F119" t="s">
         <v>156</v>
-      </c>
-      <c r="F119" t="s">
-        <v>157</v>
       </c>
       <c r="G119">
         <v>34.73673658031467</v>
@@ -5286,13 +5354,13 @@
         <v>15</v>
       </c>
       <c r="D120" t="s">
+        <v>170</v>
+      </c>
+      <c r="E120" t="s">
         <v>171</v>
       </c>
-      <c r="E120" t="s">
-        <v>172</v>
-      </c>
       <c r="F120" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G120">
         <v>35.468557804927869</v>
@@ -5312,13 +5380,13 @@
         <v>15</v>
       </c>
       <c r="D121" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E121" t="s">
+        <v>177</v>
+      </c>
+      <c r="F121" t="s">
         <v>178</v>
-      </c>
-      <c r="F121" t="s">
-        <v>179</v>
       </c>
       <c r="G121">
         <v>35.801373660598841</v>
@@ -5341,10 +5409,10 @@
         <v>106</v>
       </c>
       <c r="E122" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F122" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G122">
         <v>35.981528361118052</v>
@@ -5361,16 +5429,16 @@
         <v>8</v>
       </c>
       <c r="C123" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D123" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E123" t="s">
+        <v>179</v>
+      </c>
+      <c r="F123" t="s">
         <v>180</v>
-      </c>
-      <c r="F123" t="s">
-        <v>181</v>
       </c>
       <c r="G123">
         <v>34.731495076838243</v>
@@ -5390,13 +5458,13 @@
         <v>15</v>
       </c>
       <c r="D124" t="s">
+        <v>129</v>
+      </c>
+      <c r="E124" t="s">
         <v>130</v>
       </c>
-      <c r="E124" t="s">
-        <v>131</v>
-      </c>
       <c r="F124" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G124">
         <v>35.856719037913578</v>
@@ -5416,13 +5484,13 @@
         <v>15</v>
       </c>
       <c r="D125" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E125" t="s">
+        <v>181</v>
+      </c>
+      <c r="F125" t="s">
         <v>182</v>
-      </c>
-      <c r="F125" t="s">
-        <v>183</v>
       </c>
       <c r="G125">
         <v>35.789460510209388</v>
@@ -5439,16 +5507,16 @@
         <v>8</v>
       </c>
       <c r="C126" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D126" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E126" t="s">
+        <v>183</v>
+      </c>
+      <c r="F126" t="s">
         <v>184</v>
-      </c>
-      <c r="F126" t="s">
-        <v>185</v>
       </c>
       <c r="G126">
         <v>35.36187570973064</v>
@@ -5468,13 +5536,13 @@
         <v>15</v>
       </c>
       <c r="D127" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E127" t="s">
+        <v>181</v>
+      </c>
+      <c r="F127" t="s">
         <v>182</v>
-      </c>
-      <c r="F127" t="s">
-        <v>183</v>
       </c>
       <c r="G127">
         <v>35.767859272950247</v>
@@ -5491,16 +5559,16 @@
         <v>8</v>
       </c>
       <c r="C128" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D128" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E128" t="s">
+        <v>185</v>
+      </c>
+      <c r="F128" t="s">
         <v>186</v>
-      </c>
-      <c r="F128" t="s">
-        <v>187</v>
       </c>
       <c r="G128">
         <v>34.461619822985377</v>
@@ -5520,13 +5588,13 @@
         <v>15</v>
       </c>
       <c r="D129" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E129" t="s">
+        <v>187</v>
+      </c>
+      <c r="F129" t="s">
         <v>188</v>
-      </c>
-      <c r="F129" t="s">
-        <v>189</v>
       </c>
       <c r="G129">
         <v>35.715799812439698</v>
@@ -5546,13 +5614,13 @@
         <v>15</v>
       </c>
       <c r="D130" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E130" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F130" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G130">
         <v>35.716332245258783</v>
@@ -5572,13 +5640,13 @@
         <v>15</v>
       </c>
       <c r="D131" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E131" t="s">
+        <v>190</v>
+      </c>
+      <c r="F131" t="s">
         <v>191</v>
-      </c>
-      <c r="F131" t="s">
-        <v>192</v>
       </c>
       <c r="G131">
         <v>35.857505350133721</v>
@@ -5598,13 +5666,13 @@
         <v>15</v>
       </c>
       <c r="D132" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E132" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F132" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G132">
         <v>35.770847648105573</v>
@@ -5627,10 +5695,10 @@
         <v>106</v>
       </c>
       <c r="E133" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F133" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G133">
         <v>35.98674749221756</v>
@@ -5647,16 +5715,16 @@
         <v>8</v>
       </c>
       <c r="C134" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D134" t="s">
-        <v>114</v>
+        <v>614</v>
       </c>
       <c r="E134" t="s">
+        <v>194</v>
+      </c>
+      <c r="F134" t="s">
         <v>195</v>
-      </c>
-      <c r="F134" t="s">
-        <v>196</v>
       </c>
       <c r="G134">
         <v>35.141807838647452</v>
@@ -5673,16 +5741,16 @@
         <v>8</v>
       </c>
       <c r="C135" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D135" t="s">
-        <v>114</v>
+        <v>610</v>
       </c>
       <c r="E135" t="s">
+        <v>196</v>
+      </c>
+      <c r="F135" t="s">
         <v>197</v>
-      </c>
-      <c r="F135" t="s">
-        <v>198</v>
       </c>
       <c r="G135">
         <v>35.22960875355632</v>
@@ -5699,16 +5767,16 @@
         <v>8</v>
       </c>
       <c r="C136" t="s">
+        <v>592</v>
+      </c>
+      <c r="D136" t="s">
         <v>596</v>
       </c>
-      <c r="D136" t="s">
+      <c r="E136" t="s">
+        <v>198</v>
+      </c>
+      <c r="F136" t="s">
         <v>199</v>
-      </c>
-      <c r="E136" t="s">
-        <v>200</v>
-      </c>
-      <c r="F136" t="s">
-        <v>201</v>
       </c>
       <c r="G136">
         <v>35.161264517951302</v>
@@ -5725,16 +5793,16 @@
         <v>8</v>
       </c>
       <c r="C137" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D137" t="s">
-        <v>199</v>
+        <v>596</v>
       </c>
       <c r="E137" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F137" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G137">
         <v>35.140081559006127</v>
@@ -5751,16 +5819,16 @@
         <v>8</v>
       </c>
       <c r="C138" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D138" t="s">
-        <v>114</v>
+        <v>615</v>
       </c>
       <c r="E138" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F138" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G138">
         <v>35.22877957107066</v>
@@ -5783,10 +5851,10 @@
         <v>106</v>
       </c>
       <c r="E139" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F139" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G139">
         <v>35.99951037492842</v>
@@ -5803,16 +5871,16 @@
         <v>8</v>
       </c>
       <c r="C140" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D140" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E140" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F140" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G140">
         <v>34.879354761212923</v>
@@ -5832,13 +5900,13 @@
         <v>15</v>
       </c>
       <c r="D141" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E141" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F141" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G141">
         <v>35.910046810156523</v>
@@ -5855,16 +5923,16 @@
         <v>8</v>
       </c>
       <c r="C142" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="D142" t="s">
-        <v>199</v>
+        <v>597</v>
       </c>
       <c r="E142" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F142" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G142">
         <v>35.176200916670872</v>
@@ -5884,13 +5952,13 @@
         <v>15</v>
       </c>
       <c r="D143" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E143" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F143" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G143">
         <v>35.894904413198731</v>
@@ -5907,16 +5975,16 @@
         <v>8</v>
       </c>
       <c r="C144" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="D144" t="s">
-        <v>199</v>
+        <v>596</v>
       </c>
       <c r="E144" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F144" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G144">
         <v>35.112243001331038</v>
@@ -5936,13 +6004,13 @@
         <v>15</v>
       </c>
       <c r="D145" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E145" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F145" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G145">
         <v>35.757748986056647</v>
@@ -5959,16 +6027,16 @@
         <v>8</v>
       </c>
       <c r="C146" t="s">
+        <v>592</v>
+      </c>
+      <c r="D146" t="s">
         <v>596</v>
       </c>
-      <c r="D146" t="s">
-        <v>199</v>
-      </c>
       <c r="E146" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F146" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G146">
         <v>35.127122274147453</v>
@@ -5988,13 +6056,13 @@
         <v>15</v>
       </c>
       <c r="D147" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E147" t="s">
+        <v>190</v>
+      </c>
+      <c r="F147" t="s">
         <v>191</v>
-      </c>
-      <c r="F147" t="s">
-        <v>192</v>
       </c>
       <c r="G147">
         <v>35.857046668953103</v>
@@ -6011,16 +6079,16 @@
         <v>8</v>
       </c>
       <c r="C148" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="D148" t="s">
-        <v>114</v>
+        <v>613</v>
       </c>
       <c r="E148" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F148" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G148">
         <v>35.20661597947182</v>
@@ -6037,16 +6105,16 @@
         <v>8</v>
       </c>
       <c r="C149" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="D149" t="s">
-        <v>199</v>
+        <v>598</v>
       </c>
       <c r="E149" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F149" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G149">
         <v>35.151665295766357</v>
@@ -6063,16 +6131,16 @@
         <v>8</v>
       </c>
       <c r="C150" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D150" t="s">
-        <v>199</v>
+        <v>598</v>
       </c>
       <c r="E150" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F150" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G150">
         <v>35.153912805108902</v>
@@ -6092,13 +6160,13 @@
         <v>15</v>
       </c>
       <c r="D151" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E151" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F151" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G151">
         <v>35.757129352069008</v>
@@ -6118,13 +6186,13 @@
         <v>15</v>
       </c>
       <c r="D152" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E152" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F152" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G152">
         <v>35.895908659918057</v>
@@ -6141,16 +6209,16 @@
         <v>8</v>
       </c>
       <c r="C153" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D153" t="s">
-        <v>199</v>
+        <v>598</v>
       </c>
       <c r="E153" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F153" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G153">
         <v>35.162637841202979</v>
@@ -6167,16 +6235,16 @@
         <v>8</v>
       </c>
       <c r="C154" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D154" t="s">
-        <v>199</v>
+        <v>596</v>
       </c>
       <c r="E154" t="s">
+        <v>219</v>
+      </c>
+      <c r="F154" t="s">
         <v>221</v>
-      </c>
-      <c r="F154" t="s">
-        <v>223</v>
       </c>
       <c r="G154">
         <v>35.160508078663398</v>
@@ -6196,13 +6264,13 @@
         <v>15</v>
       </c>
       <c r="D155" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E155" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F155" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G155">
         <v>35.818784776389052</v>
@@ -6222,13 +6290,13 @@
         <v>15</v>
       </c>
       <c r="D156" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E156" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F156" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G156">
         <v>35.598527020867877</v>
@@ -6245,16 +6313,16 @@
         <v>8</v>
       </c>
       <c r="C157" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D157" t="s">
-        <v>228</v>
+        <v>601</v>
       </c>
       <c r="E157" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F157" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G157">
         <v>35.187874951825862</v>
@@ -6271,16 +6339,16 @@
         <v>8</v>
       </c>
       <c r="C158" t="s">
+        <v>592</v>
+      </c>
+      <c r="D158" t="s">
         <v>596</v>
       </c>
-      <c r="D158" t="s">
-        <v>199</v>
-      </c>
       <c r="E158" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F158" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G158">
         <v>35.157966978675688</v>
@@ -6300,13 +6368,13 @@
         <v>15</v>
       </c>
       <c r="D159" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E159" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F159" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G159">
         <v>35.796339024142</v>
@@ -6323,16 +6391,16 @@
         <v>8</v>
       </c>
       <c r="C160" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D160" t="s">
-        <v>228</v>
+        <v>602</v>
       </c>
       <c r="E160" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F160" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G160">
         <v>35.209728054198287</v>
@@ -6349,16 +6417,16 @@
         <v>8</v>
       </c>
       <c r="C161" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D161" t="s">
-        <v>228</v>
+        <v>601</v>
       </c>
       <c r="E161" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F161" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G161">
         <v>35.173520791462238</v>
@@ -6375,16 +6443,16 @@
         <v>8</v>
       </c>
       <c r="C162" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="D162" t="s">
-        <v>228</v>
+        <v>603</v>
       </c>
       <c r="E162" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F162" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G162">
         <v>35.199804229904387</v>
@@ -6401,16 +6469,16 @@
         <v>8</v>
       </c>
       <c r="C163" t="s">
+        <v>592</v>
+      </c>
+      <c r="D163" t="s">
         <v>596</v>
       </c>
-      <c r="D163" t="s">
-        <v>199</v>
-      </c>
       <c r="E163" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F163" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="G163">
         <v>35.134432328443857</v>
@@ -6430,13 +6498,13 @@
         <v>15</v>
       </c>
       <c r="D164" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E164" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F164" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G164">
         <v>36.044774326698104</v>
@@ -6453,16 +6521,16 @@
         <v>8</v>
       </c>
       <c r="C165" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D165" t="s">
-        <v>199</v>
+        <v>596</v>
       </c>
       <c r="E165" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F165" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G165">
         <v>35.134549871694567</v>
@@ -6482,13 +6550,13 @@
         <v>15</v>
       </c>
       <c r="D166" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E166" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F166" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="G166">
         <v>36.044839697224702</v>
@@ -6505,16 +6573,16 @@
         <v>8</v>
       </c>
       <c r="C167" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D167" t="s">
-        <v>249</v>
+        <v>599</v>
       </c>
       <c r="E167" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="F167" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="G167">
         <v>35.085923917362393</v>
@@ -6534,13 +6602,13 @@
         <v>15</v>
       </c>
       <c r="D168" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E168" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F168" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="G168">
         <v>35.793621207904494</v>
@@ -6560,13 +6628,13 @@
         <v>15</v>
       </c>
       <c r="D169" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E169" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F169" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="G169">
         <v>36.03685682824792</v>
@@ -6583,16 +6651,16 @@
         <v>8</v>
       </c>
       <c r="C170" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D170" t="s">
-        <v>249</v>
+        <v>600</v>
       </c>
       <c r="E170" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F170" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G170">
         <v>35.109406446382081</v>
@@ -6609,16 +6677,16 @@
         <v>8</v>
       </c>
       <c r="C171" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D171" t="s">
-        <v>228</v>
+        <v>604</v>
       </c>
       <c r="E171" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F171" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="G171">
         <v>35.186399270159868</v>
@@ -6638,13 +6706,13 @@
         <v>15</v>
       </c>
       <c r="D172" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E172" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="F172" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G172">
         <v>35.809999560778522</v>
@@ -6661,16 +6729,16 @@
         <v>8</v>
       </c>
       <c r="C173" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D173" t="s">
-        <v>228</v>
+        <v>605</v>
       </c>
       <c r="E173" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F173" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G173">
         <v>35.172984755817978</v>
@@ -6687,16 +6755,16 @@
         <v>8</v>
       </c>
       <c r="C174" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="D174" t="s">
-        <v>228</v>
+        <v>603</v>
       </c>
       <c r="E174" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F174" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="G174">
         <v>35.172896640031368</v>
@@ -6716,13 +6784,13 @@
         <v>15</v>
       </c>
       <c r="D175" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E175" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="F175" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="G175">
         <v>35.79550110143424</v>
@@ -6742,13 +6810,13 @@
         <v>15</v>
       </c>
       <c r="D176" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E176" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="F176" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="G176">
         <v>35.797053073040871</v>
@@ -6768,13 +6836,13 @@
         <v>15</v>
       </c>
       <c r="D177" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E177" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="F177" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="G177">
         <v>35.799872774861683</v>
@@ -6791,16 +6859,16 @@
         <v>8</v>
       </c>
       <c r="C178" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D178" t="s">
-        <v>228</v>
+        <v>604</v>
       </c>
       <c r="E178" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F178" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G178">
         <v>35.173102243384882</v>
@@ -6817,16 +6885,16 @@
         <v>8</v>
       </c>
       <c r="C179" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D179" t="s">
-        <v>228</v>
+        <v>601</v>
       </c>
       <c r="E179" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="F179" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="G179">
         <v>35.200083170523342</v>
@@ -6843,16 +6911,16 @@
         <v>8</v>
       </c>
       <c r="C180" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D180" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E180" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F180" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="G180">
         <v>34.923957005323601</v>
@@ -6869,16 +6937,16 @@
         <v>8</v>
       </c>
       <c r="C181" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="D181" t="s">
-        <v>228</v>
+        <v>606</v>
       </c>
       <c r="E181" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="F181" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="G181">
         <v>35.200655729845209</v>
@@ -6898,13 +6966,13 @@
         <v>15</v>
       </c>
       <c r="D182" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E182" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="F182" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="G182">
         <v>35.802575805906557</v>
@@ -6921,16 +6989,16 @@
         <v>8</v>
       </c>
       <c r="C183" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="D183" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E183" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="F183" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="G183">
         <v>34.702217752416232</v>
@@ -6950,13 +7018,13 @@
         <v>15</v>
       </c>
       <c r="D184" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E184" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="F184" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="G184">
         <v>35.799705198480787</v>
@@ -6973,16 +7041,16 @@
         <v>8</v>
       </c>
       <c r="C185" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="D185" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E185" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F185" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="G185">
         <v>34.940210832869823</v>
@@ -6999,16 +7067,16 @@
         <v>8</v>
       </c>
       <c r="C186" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D186" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E186" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F186" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="G186">
         <v>34.921504290480641</v>
@@ -7028,13 +7096,13 @@
         <v>15</v>
       </c>
       <c r="D187" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E187" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="F187" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="G187">
         <v>35.795471956137533</v>
@@ -7054,13 +7122,13 @@
         <v>15</v>
       </c>
       <c r="D188" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E188" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F188" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="G188">
         <v>35.827168432951481</v>
@@ -7080,13 +7148,13 @@
         <v>15</v>
       </c>
       <c r="D189" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E189" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F189" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G189">
         <v>35.787828233058733</v>
@@ -7106,13 +7174,13 @@
         <v>15</v>
       </c>
       <c r="D190" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E190" t="s">
+        <v>274</v>
+      </c>
+      <c r="F190" t="s">
         <v>278</v>
-      </c>
-      <c r="F190" t="s">
-        <v>282</v>
       </c>
       <c r="G190">
         <v>35.835383702898113</v>
@@ -7129,16 +7197,16 @@
         <v>8</v>
       </c>
       <c r="C191" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D191" t="s">
-        <v>249</v>
+        <v>599</v>
       </c>
       <c r="E191" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="F191" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G191">
         <v>35.09644963057238</v>
@@ -7158,13 +7226,13 @@
         <v>15</v>
       </c>
       <c r="D192" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E192" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="F192" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="G192">
         <v>35.532717081622778</v>
@@ -7184,13 +7252,13 @@
         <v>15</v>
       </c>
       <c r="D193" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E193" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F193" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G193">
         <v>35.748439388317649</v>
@@ -7210,13 +7278,13 @@
         <v>15</v>
       </c>
       <c r="D194" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E194" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="F194" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="G194">
         <v>35.801803520707537</v>
@@ -7236,13 +7304,13 @@
         <v>15</v>
       </c>
       <c r="D195" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E195" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F195" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="G195">
         <v>36.071106990911787</v>
@@ -7262,13 +7330,13 @@
         <v>15</v>
       </c>
       <c r="D196" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E196" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F196" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G196">
         <v>35.748308156760153</v>
@@ -7285,16 +7353,16 @@
         <v>8</v>
       </c>
       <c r="C197" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D197" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E197" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F197" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="G197">
         <v>34.929178907733913</v>
@@ -7311,16 +7379,16 @@
         <v>8</v>
       </c>
       <c r="C198" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D198" t="s">
-        <v>249</v>
+        <v>600</v>
       </c>
       <c r="E198" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="F198" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="G198">
         <v>35.121744006205518</v>
@@ -7337,16 +7405,16 @@
         <v>8</v>
       </c>
       <c r="C199" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D199" t="s">
-        <v>228</v>
+        <v>601</v>
       </c>
       <c r="E199" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="F199" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="G199">
         <v>35.182096881110162</v>
@@ -7363,16 +7431,16 @@
         <v>8</v>
       </c>
       <c r="C200" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="D200" t="s">
-        <v>228</v>
+        <v>602</v>
       </c>
       <c r="E200" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F200" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="G200">
         <v>35.165164107905397</v>
@@ -7392,13 +7460,13 @@
         <v>15</v>
       </c>
       <c r="D201" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E201" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="F201" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="G201">
         <v>35.812134035056197</v>
@@ -7418,13 +7486,13 @@
         <v>15</v>
       </c>
       <c r="D202" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E202" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="F202" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="G202">
         <v>35.812126750258606</v>
@@ -7444,13 +7512,13 @@
         <v>15</v>
       </c>
       <c r="D203" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E203" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="F203" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="G203">
         <v>35.7449689698919</v>
@@ -7467,16 +7535,16 @@
         <v>8</v>
       </c>
       <c r="C204" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D204" t="s">
-        <v>228</v>
+        <v>603</v>
       </c>
       <c r="E204" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F204" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="G204">
         <v>35.17788971731251</v>
@@ -7496,13 +7564,13 @@
         <v>15</v>
       </c>
       <c r="D205" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E205" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F205" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="G205">
         <v>35.85690833601268</v>
@@ -7519,16 +7587,16 @@
         <v>8</v>
       </c>
       <c r="C206" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D206" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E206" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="F206" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G206">
         <v>34.927197717313057</v>
@@ -7548,13 +7616,13 @@
         <v>15</v>
       </c>
       <c r="D207" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E207" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F207" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="G207">
         <v>35.771612945633613</v>
@@ -7571,16 +7639,16 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D208" t="s">
-        <v>228</v>
+        <v>601</v>
       </c>
       <c r="E208" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="F208" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="G208">
         <v>35.201096157346271</v>
@@ -7600,13 +7668,13 @@
         <v>15</v>
       </c>
       <c r="D209" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E209" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="F209" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="G209">
         <v>35.49139569268371</v>
@@ -7626,13 +7694,13 @@
         <v>15</v>
       </c>
       <c r="D210" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E210" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="F210" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G210">
         <v>35.537344396038648</v>
@@ -7652,13 +7720,13 @@
         <v>15</v>
       </c>
       <c r="D211" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E211" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="F211" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G211">
         <v>35.908489772758593</v>
@@ -7675,16 +7743,16 @@
         <v>8</v>
       </c>
       <c r="C212" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="D212" t="s">
-        <v>228</v>
+        <v>603</v>
       </c>
       <c r="E212" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F212" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="G212">
         <v>35.166559395990518</v>
@@ -7704,13 +7772,13 @@
         <v>15</v>
       </c>
       <c r="D213" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E213" t="s">
+        <v>307</v>
+      </c>
+      <c r="F213" t="s">
         <v>311</v>
-      </c>
-      <c r="F213" t="s">
-        <v>315</v>
       </c>
       <c r="G213">
         <v>35.88447550409623</v>
@@ -7730,13 +7798,13 @@
         <v>15</v>
       </c>
       <c r="D214" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E214" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="F214" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="G214">
         <v>35.835922618182963</v>
@@ -7753,16 +7821,16 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D215" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E215" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F215" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="G215">
         <v>34.834448111255007</v>
@@ -7782,13 +7850,13 @@
         <v>15</v>
       </c>
       <c r="D216" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E216" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F216" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G216">
         <v>35.847238993518701</v>
@@ -7808,13 +7876,13 @@
         <v>15</v>
       </c>
       <c r="D217" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E217" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="F217" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="G217">
         <v>35.876549196879083</v>
@@ -7831,16 +7899,16 @@
         <v>8</v>
       </c>
       <c r="C218" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="D218" t="s">
-        <v>228</v>
+        <v>601</v>
       </c>
       <c r="E218" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F218" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="G218">
         <v>35.159523962652933</v>
@@ -7857,16 +7925,16 @@
         <v>8</v>
       </c>
       <c r="C219" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D219" t="s">
-        <v>228</v>
+        <v>605</v>
       </c>
       <c r="E219" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="F219" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="G219">
         <v>35.214454656505779</v>
@@ -7883,16 +7951,16 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="D220" t="s">
-        <v>228</v>
+        <v>607</v>
       </c>
       <c r="E220" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="F220" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="G220">
         <v>35.216003219460227</v>
@@ -7912,13 +7980,13 @@
         <v>15</v>
       </c>
       <c r="D221" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E221" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F221" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="G221">
         <v>35.83668728899417</v>
@@ -7938,13 +8006,13 @@
         <v>15</v>
       </c>
       <c r="D222" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E222" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F222" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="G222">
         <v>35.796572183671707</v>
@@ -7964,13 +8032,13 @@
         <v>15</v>
       </c>
       <c r="D223" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E223" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="F223" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="G223">
         <v>35.737830805970987</v>
@@ -7987,16 +8055,16 @@
         <v>8</v>
       </c>
       <c r="C224" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D224" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="E224" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F224" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G224">
         <v>35.228926329649909</v>
@@ -8016,13 +8084,13 @@
         <v>15</v>
       </c>
       <c r="D225" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E225" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F225" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="G225">
         <v>35.663173535988577</v>
@@ -8039,16 +8107,16 @@
         <v>8</v>
       </c>
       <c r="C226" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D226" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E226" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F226" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="G226">
         <v>34.876812278498008</v>
@@ -8065,16 +8133,16 @@
         <v>8</v>
       </c>
       <c r="C227" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="D227" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E227" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="F227" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="G227">
         <v>35.083027637847252</v>
@@ -8094,13 +8162,13 @@
         <v>15</v>
       </c>
       <c r="D228" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E228" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="F228" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="G228">
         <v>35.753374995899122</v>
@@ -8120,13 +8188,13 @@
         <v>15</v>
       </c>
       <c r="D229" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E229" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F229" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="G229">
         <v>35.771248519157808</v>
@@ -8143,16 +8211,16 @@
         <v>8</v>
       </c>
       <c r="C230" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="D230" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E230" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="F230" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="G230">
         <v>34.950733229043593</v>
@@ -8169,16 +8237,16 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D231" t="s">
-        <v>228</v>
+        <v>601</v>
       </c>
       <c r="E231" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F231" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="G231">
         <v>35.161896102647383</v>
@@ -8195,16 +8263,16 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D232" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E232" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F232" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="G232">
         <v>34.881042336749772</v>
@@ -8224,13 +8292,13 @@
         <v>15</v>
       </c>
       <c r="D233" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E233" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F233" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="G233">
         <v>35.736343304110207</v>
@@ -8247,16 +8315,16 @@
         <v>8</v>
       </c>
       <c r="C234" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D234" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E234" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="F234" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="G234">
         <v>34.756252719550901</v>
@@ -8273,16 +8341,16 @@
         <v>8</v>
       </c>
       <c r="C235" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D235" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E235" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F235" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G235">
         <v>34.90669069177423</v>
@@ -8305,10 +8373,10 @@
         <v>19</v>
       </c>
       <c r="E236" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F236" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="G236">
         <v>35.475617614222472</v>
@@ -8325,16 +8393,16 @@
         <v>8</v>
       </c>
       <c r="C237" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D237" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="E237" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="F237" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="G237">
         <v>35.385739893652669</v>
@@ -8354,13 +8422,13 @@
         <v>15</v>
       </c>
       <c r="D238" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E238" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="F238" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="G238">
         <v>35.597745452367121</v>
@@ -8380,13 +8448,13 @@
         <v>15</v>
       </c>
       <c r="D239" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E239" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="F239" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="G239">
         <v>35.77743625414611</v>
@@ -8406,13 +8474,13 @@
         <v>15</v>
       </c>
       <c r="D240" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E240" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="F240" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="G240">
         <v>35.761707239888878</v>
@@ -8432,13 +8500,13 @@
         <v>15</v>
       </c>
       <c r="D241" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E241" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="F241" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="G241">
         <v>35.590652551949468</v>
@@ -8458,13 +8526,13 @@
         <v>15</v>
       </c>
       <c r="D242" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E242" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F242" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="G242">
         <v>35.718235845829888</v>
@@ -8487,10 +8555,10 @@
         <v>19</v>
       </c>
       <c r="E243" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F243" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="G243">
         <v>35.47936308518625</v>
@@ -8513,10 +8581,10 @@
         <v>19</v>
       </c>
       <c r="E244" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F244" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="G244">
         <v>35.479787365815277</v>
@@ -8536,13 +8604,13 @@
         <v>15</v>
       </c>
       <c r="D245" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E245" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="F245" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="G245">
         <v>35.770541527032258</v>
@@ -8559,16 +8627,16 @@
         <v>8</v>
       </c>
       <c r="C246" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="D246" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="E246" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F246" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="G246">
         <v>35.324050669863169</v>
@@ -8588,13 +8656,13 @@
         <v>15</v>
       </c>
       <c r="D247" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E247" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="F247" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="G247">
         <v>35.785110125736608</v>
@@ -8611,16 +8679,16 @@
         <v>8</v>
       </c>
       <c r="C248" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D248" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E248" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="F248" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="G248">
         <v>34.759824766141321</v>
@@ -8640,13 +8708,13 @@
         <v>15</v>
       </c>
       <c r="D249" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E249" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F249" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="G249">
         <v>35.720722856982519</v>
@@ -8663,16 +8731,16 @@
         <v>8</v>
       </c>
       <c r="C250" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D250" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E250" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F250" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="G250">
         <v>34.928103620728123</v>
@@ -8692,13 +8760,13 @@
         <v>15</v>
       </c>
       <c r="D251" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E251" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="F251" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="G251">
         <v>35.82138518857559</v>
@@ -8715,16 +8783,16 @@
         <v>8</v>
       </c>
       <c r="C252" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D252" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E252" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F252" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="G252">
         <v>34.92489240578783</v>
@@ -8747,10 +8815,10 @@
         <v>19</v>
       </c>
       <c r="E253" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F253" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="G253">
         <v>35.471184272707077</v>
@@ -8770,13 +8838,13 @@
         <v>15</v>
       </c>
       <c r="D254" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E254" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="F254" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="G254">
         <v>35.771904485611877</v>
@@ -8796,13 +8864,13 @@
         <v>15</v>
       </c>
       <c r="D255" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E255" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F255" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="G255">
         <v>35.721882463211948</v>
@@ -8822,13 +8890,13 @@
         <v>15</v>
       </c>
       <c r="D256" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E256" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="F256" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="G256">
         <v>35.756655511057858</v>
@@ -8848,13 +8916,13 @@
         <v>15</v>
       </c>
       <c r="D257" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E257" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="F257" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="G257">
         <v>35.794087542230407</v>
@@ -8877,10 +8945,10 @@
         <v>19</v>
       </c>
       <c r="E258" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="F258" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="G258">
         <v>35.473700919009048</v>
@@ -8900,13 +8968,13 @@
         <v>15</v>
       </c>
       <c r="D259" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E259" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F259" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="G259">
         <v>35.719322555266842</v>
@@ -8926,13 +8994,13 @@
         <v>15</v>
       </c>
       <c r="D260" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E260" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F260" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="G260">
         <v>35.68537229799432</v>
@@ -8952,13 +9020,13 @@
         <v>15</v>
       </c>
       <c r="D261" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E261" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F261" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="G261">
         <v>35.745107497896342</v>
@@ -8975,16 +9043,16 @@
         <v>8</v>
       </c>
       <c r="C262" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D262" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E262" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F262" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="G262">
         <v>34.910985510958838</v>
@@ -9001,16 +9069,16 @@
         <v>8</v>
       </c>
       <c r="C263" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="D263" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E263" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F263" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="G263">
         <v>34.884712141232967</v>
@@ -9027,16 +9095,16 @@
         <v>8</v>
       </c>
       <c r="C264" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D264" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E264" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F264" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="G264">
         <v>34.875161465006599</v>
@@ -9056,13 +9124,13 @@
         <v>15</v>
       </c>
       <c r="D265" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E265" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="F265" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="G265">
         <v>36.020779678546361</v>
@@ -9082,13 +9150,13 @@
         <v>15</v>
       </c>
       <c r="D266" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E266" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F266" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="G266">
         <v>35.739019329152377</v>
@@ -9108,13 +9176,13 @@
         <v>15</v>
       </c>
       <c r="D267" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E267" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="F267" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="G267">
         <v>35.892146307758487</v>
@@ -9137,10 +9205,10 @@
         <v>19</v>
       </c>
       <c r="E268" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="F268" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="G268">
         <v>35.43046804350368</v>
@@ -9157,16 +9225,16 @@
         <v>8</v>
       </c>
       <c r="C269" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D269" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E269" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F269" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="G269">
         <v>34.900892697896481</v>
@@ -9186,13 +9254,13 @@
         <v>15</v>
       </c>
       <c r="D270" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E270" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="F270" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="G270">
         <v>35.79120205466684</v>
@@ -9212,13 +9280,13 @@
         <v>15</v>
       </c>
       <c r="D271" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E271" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="F271" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="G271">
         <v>35.763026614070299</v>
@@ -9235,16 +9303,16 @@
         <v>8</v>
       </c>
       <c r="C272" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D272" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="E272" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="F272" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="G272">
         <v>35.261140747869852</v>
@@ -9261,16 +9329,16 @@
         <v>8</v>
       </c>
       <c r="C273" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D273" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="E273" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="F273" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="G273">
         <v>35.242537033685792</v>
@@ -9290,13 +9358,13 @@
         <v>15</v>
       </c>
       <c r="D274" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E274" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="F274" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="G274">
         <v>35.79054624742632</v>
@@ -9313,16 +9381,16 @@
         <v>8</v>
       </c>
       <c r="C275" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="D275" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E275" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="F275" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="G275">
         <v>34.74721858987705</v>
@@ -9342,13 +9410,13 @@
         <v>15</v>
       </c>
       <c r="D276" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E276" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="F276" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="G276">
         <v>35.902668800843642</v>
@@ -9365,16 +9433,16 @@
         <v>8</v>
       </c>
       <c r="C277" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D277" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E277" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="F277" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="G277">
         <v>34.831019397187021</v>
@@ -9397,10 +9465,10 @@
         <v>19</v>
       </c>
       <c r="E278" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="F278" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="G278">
         <v>35.420256485362501</v>
@@ -9417,16 +9485,16 @@
         <v>8</v>
       </c>
       <c r="C279" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D279" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E279" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="F279" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="G279">
         <v>34.799601307425043</v>
@@ -9443,16 +9511,16 @@
         <v>8</v>
       </c>
       <c r="C280" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D280" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E280" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F280" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="G280">
         <v>35.065625743379471</v>
@@ -9469,16 +9537,16 @@
         <v>8</v>
       </c>
       <c r="C281" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D281" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E281" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="F281" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="G281">
         <v>34.724185946638833</v>
@@ -9498,13 +9566,13 @@
         <v>15</v>
       </c>
       <c r="D282" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E282" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="F282" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="G282">
         <v>35.818136481094378</v>
@@ -9524,13 +9592,13 @@
         <v>15</v>
       </c>
       <c r="D283" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E283" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="F283" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="G283">
         <v>35.871228154573117</v>
@@ -9550,13 +9618,13 @@
         <v>15</v>
       </c>
       <c r="D284" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E284" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="F284" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="G284">
         <v>35.802153235690099</v>
@@ -9576,13 +9644,13 @@
         <v>15</v>
       </c>
       <c r="D285" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E285" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="F285" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="G285">
         <v>35.81363468910736</v>
@@ -9608,7 +9676,7 @@
         <v>20</v>
       </c>
       <c r="F286" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="G286">
         <v>35.371296239810952</v>
@@ -9628,13 +9696,13 @@
         <v>15</v>
       </c>
       <c r="D287" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E287" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="F287" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="G287">
         <v>35.825209169397041</v>
@@ -9654,13 +9722,13 @@
         <v>15</v>
       </c>
       <c r="D288" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E288" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="F288" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="G288">
         <v>35.812112180661472</v>
@@ -9680,13 +9748,13 @@
         <v>15</v>
       </c>
       <c r="D289" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E289" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="F289" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="G289">
         <v>36.027006058468537</v>
@@ -9706,13 +9774,13 @@
         <v>15</v>
       </c>
       <c r="D290" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E290" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="F290" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="G290">
         <v>35.799442904305472</v>
@@ -9732,13 +9800,13 @@
         <v>15</v>
       </c>
       <c r="D291" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E291" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="F291" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G291">
         <v>35.823876259855332</v>
@@ -9758,13 +9826,13 @@
         <v>15</v>
       </c>
       <c r="D292" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E292" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="F292" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="G292">
         <v>35.812439995950811</v>
@@ -9784,13 +9852,13 @@
         <v>15</v>
       </c>
       <c r="D293" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E293" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="F293" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="G293">
         <v>35.796098577660352</v>
@@ -9810,13 +9878,13 @@
         <v>15</v>
       </c>
       <c r="D294" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E294" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="F294" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="G294">
         <v>35.808389560994407</v>
@@ -9836,13 +9904,13 @@
         <v>15</v>
       </c>
       <c r="D295" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E295" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F295" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="G295">
         <v>35.83583522676382</v>
@@ -9862,13 +9930,13 @@
         <v>15</v>
       </c>
       <c r="D296" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E296" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="F296" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="G296">
         <v>36.077743232721318</v>
@@ -9888,13 +9956,13 @@
         <v>15</v>
       </c>
       <c r="D297" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E297" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="F297" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="G297">
         <v>35.834961307278022</v>
@@ -9914,13 +9982,13 @@
         <v>15</v>
       </c>
       <c r="D298" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E298" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="F298" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="G298">
         <v>35.846139468019018</v>
@@ -9937,16 +10005,16 @@
         <v>8</v>
       </c>
       <c r="C299" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="D299" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E299" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="F299" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G299">
         <v>35.225580168071701</v>
@@ -9966,13 +10034,13 @@
         <v>15</v>
       </c>
       <c r="D300" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E300" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="F300" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="G300">
         <v>35.823133316952983</v>
@@ -9992,13 +10060,13 @@
         <v>15</v>
       </c>
       <c r="D301" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E301" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="F301" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="G301">
         <v>35.818901323296338</v>
@@ -10024,7 +10092,7 @@
         <v>17</v>
       </c>
       <c r="F302" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="G302">
         <v>35.649757879712922</v>
@@ -10044,13 +10112,13 @@
         <v>15</v>
       </c>
       <c r="D303" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E303" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="F303" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="G303">
         <v>35.760402422907461</v>
@@ -10070,13 +10138,13 @@
         <v>15</v>
       </c>
       <c r="D304" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E304" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="F304" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="G304">
         <v>36.069342556684603</v>
@@ -10096,13 +10164,13 @@
         <v>15</v>
       </c>
       <c r="D305" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E305" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="F305" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="G305">
         <v>35.79693649406714</v>
@@ -10119,16 +10187,16 @@
         <v>8</v>
       </c>
       <c r="C306" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D306" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E306" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F306" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="G306">
         <v>35.290277492847508</v>
@@ -10148,13 +10216,13 @@
         <v>15</v>
       </c>
       <c r="D307" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E307" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="F307" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="G307">
         <v>35.988324793990053</v>
@@ -10171,16 +10239,16 @@
         <v>8</v>
       </c>
       <c r="C308" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D308" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E308" t="s">
+        <v>428</v>
+      </c>
+      <c r="F308" t="s">
         <v>432</v>
-      </c>
-      <c r="F308" t="s">
-        <v>436</v>
       </c>
       <c r="G308">
         <v>35.322592124200007</v>
@@ -10197,16 +10265,16 @@
         <v>8</v>
       </c>
       <c r="C309" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D309" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E309" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="F309" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="G309">
         <v>34.846790299615293</v>
@@ -10229,10 +10297,10 @@
         <v>19</v>
       </c>
       <c r="E310" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="F310" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="G310">
         <v>35.460919344326101</v>
@@ -10255,10 +10323,10 @@
         <v>19</v>
       </c>
       <c r="E311" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="F311" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="G311">
         <v>35.454560723830333</v>
@@ -10275,16 +10343,16 @@
         <v>8</v>
       </c>
       <c r="C312" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D312" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E312" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="F312" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="G312">
         <v>34.843281000660113</v>
@@ -10304,13 +10372,13 @@
         <v>15</v>
       </c>
       <c r="D313" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E313" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="F313" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="G313">
         <v>35.709271751040667</v>
@@ -10330,13 +10398,13 @@
         <v>15</v>
       </c>
       <c r="D314" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E314" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="F314" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="G314">
         <v>35.903352787243122</v>
@@ -10353,16 +10421,16 @@
         <v>8</v>
       </c>
       <c r="C315" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D315" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E315" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="F315" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="G315">
         <v>35.229528037049498</v>
@@ -10379,16 +10447,16 @@
         <v>8</v>
       </c>
       <c r="C316" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D316" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E316" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="F316" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="G316">
         <v>35.144518391102068</v>
@@ -10405,16 +10473,16 @@
         <v>8</v>
       </c>
       <c r="C317" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D317" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E317" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="F317" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="G317">
         <v>35.134953925324538</v>
@@ -10434,13 +10502,13 @@
         <v>15</v>
       </c>
       <c r="D318" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E318" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="F318" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G318">
         <v>35.805715869337902</v>
@@ -10457,16 +10525,16 @@
         <v>8</v>
       </c>
       <c r="C319" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D319" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="E319" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="F319" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="G319">
         <v>34.657465828434347</v>
@@ -10486,13 +10554,13 @@
         <v>15</v>
       </c>
       <c r="D320" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E320" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="F320" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="G320">
         <v>35.417723525776992</v>
@@ -10515,10 +10583,10 @@
         <v>16</v>
       </c>
       <c r="E321" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="F321" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="G321">
         <v>35.692033640825571</v>
@@ -10535,16 +10603,16 @@
         <v>8</v>
       </c>
       <c r="C322" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D322" t="s">
         <v>22</v>
       </c>
       <c r="E322" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="F322" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="G322">
         <v>34.96693021923528</v>
@@ -10561,16 +10629,16 @@
         <v>8</v>
       </c>
       <c r="C323" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D323" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E323" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="F323" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="G323">
         <v>34.830680204808793</v>
@@ -10590,13 +10658,13 @@
         <v>15</v>
       </c>
       <c r="D324" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E324" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="F324" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="G324">
         <v>36.088313594814878</v>
@@ -10613,16 +10681,16 @@
         <v>8</v>
       </c>
       <c r="C325" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="D325" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E325" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="F325" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="G325">
         <v>35.211827169314972</v>
@@ -10639,16 +10707,16 @@
         <v>8</v>
       </c>
       <c r="C326" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D326" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E326" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="F326" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="G326">
         <v>35.218836059121543</v>
@@ -10668,13 +10736,13 @@
         <v>15</v>
       </c>
       <c r="D327" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E327" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="F327" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="G327">
         <v>35.839964366134403</v>
@@ -10694,13 +10762,13 @@
         <v>15</v>
       </c>
       <c r="D328" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E328" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="F328" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="G328">
         <v>35.844166109190908</v>
@@ -10717,16 +10785,16 @@
         <v>8</v>
       </c>
       <c r="C329" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D329" t="s">
         <v>22</v>
       </c>
       <c r="E329" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="F329" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="G329">
         <v>34.906351811401549</v>
@@ -10743,16 +10811,16 @@
         <v>8</v>
       </c>
       <c r="C330" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="D330" t="s">
         <v>22</v>
       </c>
       <c r="E330" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="F330" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="G330">
         <v>35.04658748311374</v>
@@ -10775,10 +10843,10 @@
         <v>16</v>
       </c>
       <c r="E331" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="F331" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="G331">
         <v>35.670851123820512</v>
@@ -10798,13 +10866,13 @@
         <v>15</v>
       </c>
       <c r="D332" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E332" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="F332" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="G332">
         <v>35.870179918059961</v>
@@ -10821,16 +10889,16 @@
         <v>8</v>
       </c>
       <c r="C333" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D333" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E333" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="F333" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="G333">
         <v>34.883908924942823</v>
@@ -10847,16 +10915,16 @@
         <v>8</v>
       </c>
       <c r="C334" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D334" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="E334" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="F334" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="G334">
         <v>34.606390455437648</v>
@@ -10873,16 +10941,16 @@
         <v>8</v>
       </c>
       <c r="C335" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D335" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E335" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="F335" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="G335">
         <v>35.127159009729127</v>
@@ -10899,16 +10967,16 @@
         <v>8</v>
       </c>
       <c r="C336" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D336" t="s">
         <v>22</v>
       </c>
       <c r="E336" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="F336" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="G336">
         <v>35.033841355197943</v>
@@ -10925,16 +10993,16 @@
         <v>8</v>
       </c>
       <c r="C337" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D337" t="s">
         <v>22</v>
       </c>
       <c r="E337" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="F337" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="G337">
         <v>35.029619175690478</v>
@@ -10954,13 +11022,13 @@
         <v>15</v>
       </c>
       <c r="D338" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E338" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="F338" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="G338">
         <v>35.411756846735031</v>
@@ -10983,10 +11051,10 @@
         <v>16</v>
       </c>
       <c r="E339" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="F339" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="G339">
         <v>35.554389323922521</v>
@@ -11009,10 +11077,10 @@
         <v>16</v>
       </c>
       <c r="E340" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="F340" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="G340">
         <v>35.572248987514939</v>
@@ -11032,13 +11100,13 @@
         <v>15</v>
       </c>
       <c r="D341" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="E341" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="F341" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="G341">
         <v>35.706718732432961</v>
@@ -11058,13 +11126,13 @@
         <v>15</v>
       </c>
       <c r="D342" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E342" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="F342" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="G342">
         <v>36.126503148724041</v>
@@ -11084,13 +11152,13 @@
         <v>15</v>
       </c>
       <c r="D343" t="s">
+        <v>481</v>
+      </c>
+      <c r="E343" t="s">
+        <v>484</v>
+      </c>
+      <c r="F343" t="s">
         <v>485</v>
-      </c>
-      <c r="E343" t="s">
-        <v>488</v>
-      </c>
-      <c r="F343" t="s">
-        <v>489</v>
       </c>
       <c r="G343">
         <v>35.847857925008057</v>
@@ -11107,16 +11175,16 @@
         <v>8</v>
       </c>
       <c r="C344" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D344" t="s">
         <v>22</v>
       </c>
       <c r="E344" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="F344" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="G344">
         <v>35.020615054027722</v>
@@ -11139,10 +11207,10 @@
         <v>16</v>
       </c>
       <c r="E345" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="F345" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="G345">
         <v>35.637785533218732</v>
@@ -11159,16 +11227,16 @@
         <v>8</v>
       </c>
       <c r="C346" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D346" t="s">
         <v>22</v>
       </c>
       <c r="E346" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="F346" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="G346">
         <v>34.952124823434637</v>
@@ -11185,16 +11253,16 @@
         <v>8</v>
       </c>
       <c r="C347" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D347" t="s">
         <v>22</v>
       </c>
       <c r="E347" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="F347" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="G347">
         <v>35.04145396734404</v>
@@ -11214,13 +11282,13 @@
         <v>15</v>
       </c>
       <c r="D348" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E348" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="F348" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="G348">
         <v>35.317160825790779</v>
@@ -11237,16 +11305,16 @@
         <v>8</v>
       </c>
       <c r="C349" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D349" t="s">
         <v>22</v>
       </c>
       <c r="E349" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="F349" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="G349">
         <v>34.918646380117472</v>
@@ -11266,13 +11334,13 @@
         <v>15</v>
       </c>
       <c r="D350" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="E350" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="F350" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="G350">
         <v>35.983658215362397</v>
@@ -11292,13 +11360,13 @@
         <v>15</v>
       </c>
       <c r="D351" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="E351" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="F351" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="G351">
         <v>35.744487765476933</v>
@@ -11315,16 +11383,16 @@
         <v>8</v>
       </c>
       <c r="C352" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D352" t="s">
         <v>22</v>
       </c>
       <c r="E352" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="F352" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="G352">
         <v>35.021895112183941</v>
@@ -11344,13 +11412,13 @@
         <v>15</v>
       </c>
       <c r="D353" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="E353" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="F353" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="G353">
         <v>35.726294647088757</v>
@@ -11370,13 +11438,13 @@
         <v>15</v>
       </c>
       <c r="D354" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="E354" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="F354" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="G354">
         <v>35.745822006933011</v>
@@ -11396,13 +11464,13 @@
         <v>15</v>
       </c>
       <c r="D355" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="E355" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="F355" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="G355">
         <v>35.77633576169012</v>
@@ -11422,13 +11490,13 @@
         <v>15</v>
       </c>
       <c r="D356" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="E356" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="F356" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="G356">
         <v>35.783907716168343</v>
@@ -11445,16 +11513,16 @@
         <v>8</v>
       </c>
       <c r="C357" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="D357" t="s">
         <v>22</v>
       </c>
       <c r="E357" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="F357" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="G357">
         <v>35.093531674404836</v>
@@ -11471,16 +11539,16 @@
         <v>8</v>
       </c>
       <c r="C358" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="D358" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="E358" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="F358" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="G358">
         <v>35.357846376008403</v>
@@ -11500,13 +11568,13 @@
         <v>15</v>
       </c>
       <c r="D359" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="E359" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="F359" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="G359">
         <v>35.953878655942837</v>
@@ -11523,16 +11591,16 @@
         <v>8</v>
       </c>
       <c r="C360" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D360" t="s">
         <v>22</v>
       </c>
       <c r="E360" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="F360" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="G360">
         <v>35.154265349960923</v>
@@ -11552,13 +11620,13 @@
         <v>15</v>
       </c>
       <c r="D361" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E361" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="F361" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="G361">
         <v>35.388376387062408</v>
@@ -11575,16 +11643,16 @@
         <v>8</v>
       </c>
       <c r="C362" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D362" t="s">
         <v>22</v>
       </c>
       <c r="E362" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="F362" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="G362">
         <v>34.947000105186348</v>
@@ -11604,13 +11672,13 @@
         <v>15</v>
       </c>
       <c r="D363" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E363" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="F363" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="G363">
         <v>35.449826188642227</v>
@@ -11627,16 +11695,16 @@
         <v>8</v>
       </c>
       <c r="C364" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D364" t="s">
         <v>22</v>
       </c>
       <c r="E364" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="F364" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="G364">
         <v>35.083828903129543</v>
@@ -11656,13 +11724,13 @@
         <v>15</v>
       </c>
       <c r="D365" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E365" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="F365" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="G365">
         <v>35.387812477661292</v>
@@ -11679,16 +11747,16 @@
         <v>8</v>
       </c>
       <c r="C366" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D366" t="s">
         <v>22</v>
       </c>
       <c r="E366" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="F366" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="G366">
         <v>34.97271618589923</v>
@@ -11708,13 +11776,13 @@
         <v>15</v>
       </c>
       <c r="D367" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E367" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="F367" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="G367">
         <v>35.383000778676973</v>
@@ -11734,13 +11802,13 @@
         <v>15</v>
       </c>
       <c r="D368" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="E368" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="F368" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="G368">
         <v>35.619334387954538</v>
@@ -11760,13 +11828,13 @@
         <v>15</v>
       </c>
       <c r="D369" t="s">
+        <v>522</v>
+      </c>
+      <c r="E369" t="s">
+        <v>525</v>
+      </c>
+      <c r="F369" t="s">
         <v>526</v>
-      </c>
-      <c r="E369" t="s">
-        <v>529</v>
-      </c>
-      <c r="F369" t="s">
-        <v>530</v>
       </c>
       <c r="G369">
         <v>35.551268589654967</v>
@@ -11786,13 +11854,13 @@
         <v>15</v>
       </c>
       <c r="D370" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E370" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="F370" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="G370">
         <v>35.367018312652192</v>
@@ -11812,13 +11880,13 @@
         <v>15</v>
       </c>
       <c r="D371" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E371" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="F371" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="G371">
         <v>35.387438977056419</v>
@@ -11838,13 +11906,13 @@
         <v>15</v>
       </c>
       <c r="D372" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E372" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="F372" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="G372">
         <v>35.383528102157939</v>
@@ -11864,13 +11932,13 @@
         <v>15</v>
       </c>
       <c r="D373" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E373" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="F373" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="G373">
         <v>35.376848416719433</v>
@@ -11890,13 +11958,13 @@
         <v>15</v>
       </c>
       <c r="D374" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E374" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="F374" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="G374">
         <v>35.377258588778567</v>
@@ -11916,13 +11984,13 @@
         <v>15</v>
       </c>
       <c r="D375" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E375" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="F375" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="G375">
         <v>35.363633901429573</v>
@@ -11942,13 +12010,13 @@
         <v>15</v>
       </c>
       <c r="D376" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E376" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="F376" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="G376">
         <v>35.363597272826347</v>
@@ -11968,13 +12036,13 @@
         <v>15</v>
       </c>
       <c r="D377" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="E377" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="F377" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="G377">
         <v>35.951951613036883</v>
@@ -11994,13 +12062,13 @@
         <v>15</v>
       </c>
       <c r="D378" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E378" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="F378" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="G378">
         <v>35.356036773437182</v>
@@ -12020,13 +12088,13 @@
         <v>15</v>
       </c>
       <c r="D379" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="E379" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="F379" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="G379">
         <v>35.973720827063737</v>
@@ -12046,13 +12114,13 @@
         <v>15</v>
       </c>
       <c r="D380" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="E380" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="F380" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="G380">
         <v>35.483942271556423</v>
@@ -12072,13 +12140,13 @@
         <v>15</v>
       </c>
       <c r="D381" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E381" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="F381" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="G381">
         <v>35.348145846227453</v>
@@ -12098,13 +12166,13 @@
         <v>15</v>
       </c>
       <c r="D382" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E382" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="F382" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="G382">
         <v>35.972215934241049</v>
@@ -12124,13 +12192,13 @@
         <v>15</v>
       </c>
       <c r="D383" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E383" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="F383" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="G383">
         <v>35.98851377734043</v>
@@ -12150,13 +12218,13 @@
         <v>15</v>
       </c>
       <c r="D384" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E384" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="F384" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="G384">
         <v>35.995585790326601</v>
@@ -12176,13 +12244,13 @@
         <v>15</v>
       </c>
       <c r="D385" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E385" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="F385" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="G385">
         <v>35.993630692902499</v>
@@ -12202,13 +12270,13 @@
         <v>15</v>
       </c>
       <c r="D386" t="s">
+        <v>531</v>
+      </c>
+      <c r="E386" t="s">
+        <v>532</v>
+      </c>
+      <c r="F386" t="s">
         <v>535</v>
-      </c>
-      <c r="E386" t="s">
-        <v>536</v>
-      </c>
-      <c r="F386" t="s">
-        <v>539</v>
       </c>
       <c r="G386">
         <v>36.019021381828878</v>
@@ -12225,16 +12293,16 @@
         <v>8</v>
       </c>
       <c r="C387" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D387" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="E387" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="F387" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="G387">
         <v>34.991293295048663</v>
@@ -12254,13 +12322,13 @@
         <v>15</v>
       </c>
       <c r="D388" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E388" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="F388" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="G388">
         <v>36.009088448389598</v>
@@ -12280,13 +12348,13 @@
         <v>15</v>
       </c>
       <c r="D389" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E389" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="F389" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="G389">
         <v>35.904844439206471</v>
@@ -12303,16 +12371,16 @@
         <v>8</v>
       </c>
       <c r="C390" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D390" t="s">
+        <v>536</v>
+      </c>
+      <c r="E390" t="s">
         <v>540</v>
       </c>
-      <c r="E390" t="s">
-        <v>544</v>
-      </c>
       <c r="F390" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="G390">
         <v>35.101675230640133</v>
@@ -12332,13 +12400,13 @@
         <v>15</v>
       </c>
       <c r="D391" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E391" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="F391" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="G391">
         <v>35.477739093813398</v>
@@ -12358,13 +12426,13 @@
         <v>15</v>
       </c>
       <c r="D392" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E392" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="F392" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="G392">
         <v>35.451092173558273</v>
@@ -12384,13 +12452,13 @@
         <v>15</v>
       </c>
       <c r="D393" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="E393" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="F393" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="G393">
         <v>35.776875077777078</v>
@@ -12410,13 +12478,13 @@
         <v>15</v>
       </c>
       <c r="D394" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E394" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="F394" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="G394">
         <v>35.448582137820807</v>
@@ -12436,13 +12504,13 @@
         <v>15</v>
       </c>
       <c r="D395" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E395" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="F395" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="G395">
         <v>35.980423431150541</v>
@@ -12462,13 +12530,13 @@
         <v>15</v>
       </c>
       <c r="D396" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E396" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="F396" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="G396">
         <v>35.489896286669548</v>
@@ -12488,13 +12556,13 @@
         <v>15</v>
       </c>
       <c r="D397" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="E397" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="F397" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="G397">
         <v>35.72641862227951</v>
@@ -12514,13 +12582,13 @@
         <v>15</v>
       </c>
       <c r="D398" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E398" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="F398" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="G398">
         <v>35.873084372710039</v>
@@ -12537,16 +12605,16 @@
         <v>8</v>
       </c>
       <c r="C399" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D399" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="E399" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="F399" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="G399">
         <v>34.965693471062153</v>
@@ -12566,13 +12634,13 @@
         <v>15</v>
       </c>
       <c r="D400" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E400" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="F400" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="G400">
         <v>35.871053449450628</v>
@@ -12589,16 +12657,16 @@
         <v>8</v>
       </c>
       <c r="C401" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D401" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="E401" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="F401" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="G401">
         <v>35.159230194372128</v>
@@ -12618,13 +12686,13 @@
         <v>15</v>
       </c>
       <c r="D402" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E402" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="F402" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="G402">
         <v>36.01140648703543</v>
@@ -12644,13 +12712,13 @@
         <v>15</v>
       </c>
       <c r="D403" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E403" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="F403" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="G403">
         <v>35.955216650535633</v>
@@ -12670,13 +12738,13 @@
         <v>15</v>
       </c>
       <c r="D404" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E404" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="F404" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="G404">
         <v>35.893332523193408</v>
@@ -12696,13 +12764,13 @@
         <v>15</v>
       </c>
       <c r="D405" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E405" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="F405" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="G405">
         <v>35.869641235568757</v>
@@ -12719,16 +12787,16 @@
         <v>8</v>
       </c>
       <c r="C406" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D406" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="E406" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="F406" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="G406">
         <v>34.975616376737932</v>
@@ -12745,16 +12813,16 @@
         <v>8</v>
       </c>
       <c r="C407" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D407" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E407" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="F407" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="G407">
         <v>34.749809360478388</v>
@@ -12771,16 +12839,16 @@
         <v>8</v>
       </c>
       <c r="C408" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D408" t="s">
+        <v>562</v>
+      </c>
+      <c r="E408" t="s">
+        <v>565</v>
+      </c>
+      <c r="F408" t="s">
         <v>566</v>
-      </c>
-      <c r="E408" t="s">
-        <v>569</v>
-      </c>
-      <c r="F408" t="s">
-        <v>570</v>
       </c>
       <c r="G408">
         <v>34.764237949122048</v>
@@ -12797,16 +12865,16 @@
         <v>8</v>
       </c>
       <c r="C409" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D409" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="E409" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="F409" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="G409">
         <v>35.10224113347148</v>
@@ -12823,16 +12891,16 @@
         <v>8</v>
       </c>
       <c r="C410" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D410" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E410" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F410" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="G410">
         <v>34.768923930300907</v>
@@ -12849,16 +12917,16 @@
         <v>8</v>
       </c>
       <c r="C411" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="D411" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E411" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F411" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="G411">
         <v>34.74863577360756</v>
@@ -12878,13 +12946,13 @@
         <v>15</v>
       </c>
       <c r="D412" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E412" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="F412" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="G412">
         <v>35.924567982295272</v>
@@ -12901,16 +12969,16 @@
         <v>8</v>
       </c>
       <c r="C413" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D413" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E413" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F413" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="G413">
         <v>34.786802009285402</v>
@@ -12927,16 +12995,16 @@
         <v>8</v>
       </c>
       <c r="C414" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D414" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E414" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F414" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="G414">
         <v>34.749418166707642</v>
@@ -12953,16 +13021,16 @@
         <v>8</v>
       </c>
       <c r="C415" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D415" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E415" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="F415" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="G415">
         <v>34.790247318369133</v>
@@ -12979,16 +13047,16 @@
         <v>8</v>
       </c>
       <c r="C416" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D416" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E416" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="F416" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="G416">
         <v>34.757935438436689</v>
@@ -13005,16 +13073,16 @@
         <v>8</v>
       </c>
       <c r="C417" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D417" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E417" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="F417" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="G417">
         <v>34.753647389769498</v>
@@ -13031,16 +13099,16 @@
         <v>8</v>
       </c>
       <c r="C418" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D418" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="E418" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="F418" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="G418">
         <v>35.047852425998158</v>
@@ -13060,13 +13128,13 @@
         <v>15</v>
       </c>
       <c r="D419" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E419" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="F419" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="G419">
         <v>35.933013189265637</v>
@@ -13086,13 +13154,13 @@
         <v>15</v>
       </c>
       <c r="D420" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E420" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="F420" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="G420">
         <v>35.929652672325858</v>
@@ -13109,16 +13177,16 @@
         <v>8</v>
       </c>
       <c r="C421" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="D421" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="E421" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="F421" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="G421">
         <v>35.005267509297411</v>
@@ -13138,13 +13206,13 @@
         <v>15</v>
       </c>
       <c r="D422" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E422" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="F422" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="G422">
         <v>35.905695759675943</v>
@@ -13161,16 +13229,16 @@
         <v>8</v>
       </c>
       <c r="C423" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D423" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="E423" t="s">
+        <v>578</v>
+      </c>
+      <c r="F423" t="s">
         <v>582</v>
-      </c>
-      <c r="F423" t="s">
-        <v>586</v>
       </c>
       <c r="G423">
         <v>35.009395296049753</v>
@@ -13187,16 +13255,16 @@
         <v>8</v>
       </c>
       <c r="C424" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D424" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="E424" t="s">
+        <v>578</v>
+      </c>
+      <c r="F424" t="s">
         <v>582</v>
-      </c>
-      <c r="F424" t="s">
-        <v>586</v>
       </c>
       <c r="G424">
         <v>35.002309501921758</v>
@@ -13216,13 +13284,13 @@
         <v>15</v>
       </c>
       <c r="D425" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E425" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="F425" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="G425">
         <v>35.877954008880238</v>
@@ -13242,13 +13310,13 @@
         <v>15</v>
       </c>
       <c r="D426" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E426" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="F426" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="G426">
         <v>35.963629499390038</v>
@@ -13268,13 +13336,13 @@
         <v>15</v>
       </c>
       <c r="D427" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E427" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="F427" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="G427">
         <v>35.995440431590893</v>
